--- a/CO国試data/CO_questions_2016.xlsx
+++ b/CO国試data/CO_questions_2016.xlsx
@@ -542,15 +542,15 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達・加齢</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>生殖、発生の概要</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>2</v>
       </c>
@@ -599,7 +599,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>False</t>
@@ -635,15 +634,15 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達・加齢</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>遺伝</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>1</v>
       </c>
@@ -692,7 +691,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>False</t>
@@ -728,15 +726,15 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達・加齢</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>内分泌</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>2</v>
       </c>
@@ -785,7 +783,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>True</t>
@@ -821,15 +818,15 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>視能検査法と検査機器の基礎</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>3</v>
       </c>
@@ -878,7 +875,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>False</t>
@@ -914,15 +910,15 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>視覚情報処理過程の概要</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>2</v>
       </c>
@@ -971,7 +967,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>False</t>
@@ -1007,15 +1002,15 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達・加齢</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>心身の成長・発達、加齢</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>2</v>
       </c>
@@ -1064,7 +1059,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>False</t>
@@ -1100,15 +1094,15 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>2</v>
       </c>
@@ -1157,7 +1151,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>False</t>
@@ -1193,15 +1186,15 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>視覚情報処理過程の概要</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>2</v>
       </c>
@@ -1250,7 +1243,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>True</t>
@@ -1286,15 +1278,15 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>2</v>
       </c>
@@ -1343,7 +1335,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>False</t>
@@ -1379,15 +1370,15 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>視覚情報処理過程の概要</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>1</v>
       </c>
@@ -1436,7 +1427,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>False</t>
@@ -1472,15 +1462,15 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>3</v>
       </c>
@@ -1529,7 +1519,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>True</t>
@@ -1565,15 +1554,15 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>眼科薬理学</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>眼薬理学</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>2</v>
       </c>
@@ -1622,7 +1611,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>False</t>
@@ -1658,15 +1646,15 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>2</v>
       </c>
@@ -1715,7 +1703,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>False</t>
@@ -1751,15 +1738,15 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>3</v>
       </c>
@@ -1809,7 +1796,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>False</t>
@@ -1845,15 +1831,15 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>2</v>
       </c>
@@ -1902,7 +1888,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>False</t>
@@ -1938,15 +1923,15 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>3</v>
       </c>
@@ -1995,7 +1980,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>False</t>
@@ -2031,15 +2015,15 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>2</v>
       </c>
@@ -2088,7 +2072,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>True</t>
@@ -2124,15 +2107,15 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>3</v>
       </c>
@@ -2181,7 +2164,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
           <t>False</t>
@@ -2217,15 +2199,15 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>3</v>
       </c>
@@ -2275,7 +2257,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>False</t>
@@ -2311,15 +2292,15 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
         <v>1</v>
       </c>
@@ -2368,7 +2349,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>False</t>
@@ -2407,12 +2387,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>視能訓練士の役割と義務</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>2</v>
       </c>
@@ -2461,7 +2441,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>False</t>
@@ -2497,15 +2476,15 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>2</v>
       </c>
@@ -2554,7 +2533,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
           <t>False</t>
@@ -2590,15 +2568,15 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ロービジョン</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>視能矯正訓練の対象となる視能障害</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>4</v>
       </c>
@@ -2647,7 +2625,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
           <t>False</t>
@@ -2683,15 +2660,15 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
         <v>2</v>
       </c>
@@ -2740,7 +2717,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
           <t>False</t>
@@ -2776,15 +2752,15 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
         <v>4</v>
       </c>
@@ -2834,7 +2810,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
           <t>False</t>
@@ -2870,15 +2845,15 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
         <v>3</v>
       </c>
@@ -2927,7 +2902,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
           <t>False</t>
@@ -2963,15 +2937,15 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
         <v>3</v>
       </c>
@@ -3020,7 +2994,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
           <t>False</t>
@@ -3056,15 +3029,15 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
         <v>2</v>
       </c>
@@ -3113,7 +3086,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
           <t>False</t>
@@ -3149,15 +3121,15 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
         <v>2</v>
       </c>
@@ -3206,7 +3178,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
           <t>False</t>
@@ -3242,15 +3213,15 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
         <v>4</v>
       </c>
@@ -3299,7 +3270,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr">
         <is>
           <t>False</t>
@@ -3335,15 +3305,15 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
         <v>3</v>
       </c>
@@ -3392,7 +3362,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr">
         <is>
           <t>False</t>
@@ -3428,15 +3397,15 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
         <v>2</v>
       </c>
@@ -3485,7 +3454,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr">
         <is>
           <t>False</t>
@@ -3521,15 +3489,15 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
         <v>2</v>
       </c>
@@ -3578,7 +3546,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr">
         <is>
           <t>False</t>
@@ -3614,15 +3581,15 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
         <v>2</v>
       </c>
@@ -3671,7 +3638,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr">
         <is>
           <t>False</t>
@@ -3707,15 +3673,15 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
         <v>3</v>
       </c>
@@ -3764,7 +3730,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr">
         <is>
           <t>False</t>
@@ -3800,15 +3765,15 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
         <v>3</v>
       </c>
@@ -3857,7 +3822,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr">
         <is>
           <t>False</t>
@@ -3893,15 +3857,15 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>眼科薬理学</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
         <is>
           <t>眼薬理学</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
         <v>3</v>
       </c>
@@ -3950,7 +3914,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr">
         <is>
           <t>True</t>
@@ -3989,12 +3952,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>公衆衛生学</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
         <v>2</v>
       </c>
@@ -4043,7 +4006,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr">
         <is>
           <t>True</t>
@@ -4079,15 +4041,15 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
         <v>3</v>
       </c>
@@ -4177,15 +4139,15 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
         <v>1</v>
       </c>
@@ -4234,7 +4196,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr">
         <is>
           <t>False</t>
@@ -4270,15 +4231,15 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
         <v>2</v>
       </c>
@@ -4327,7 +4288,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr">
         <is>
           <t>False</t>
@@ -4363,15 +4323,15 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
         <v>2</v>
       </c>
@@ -4420,7 +4380,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr">
         <is>
           <t>False</t>
@@ -4456,15 +4415,15 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
         <v>2</v>
       </c>
@@ -4513,7 +4472,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr">
         <is>
           <t>True</t>
@@ -4549,15 +4507,15 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
         <v>2</v>
       </c>
@@ -4606,7 +4564,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr">
         <is>
           <t>False</t>
@@ -4642,15 +4599,15 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
         <v>3</v>
       </c>
@@ -4699,7 +4656,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr">
         <is>
           <t>True</t>
@@ -4735,15 +4691,15 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
         <v>3</v>
       </c>
@@ -4792,7 +4748,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr">
         <is>
           <t>True</t>
@@ -4828,15 +4783,15 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
         <v>2</v>
       </c>
@@ -4885,7 +4840,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr">
         <is>
           <t>False</t>
@@ -4921,15 +4875,15 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
         <v>2</v>
       </c>
@@ -4978,7 +4932,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr">
         <is>
           <t>False</t>
@@ -5014,15 +4967,15 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
         <v>1</v>
       </c>
@@ -5071,7 +5024,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr">
         <is>
           <t>False</t>
@@ -5107,15 +5059,15 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
         <v>4</v>
       </c>
@@ -5164,7 +5116,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr">
         <is>
           <t>False</t>
@@ -5200,15 +5151,15 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
         <v>3</v>
       </c>
@@ -5257,7 +5208,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr">
         <is>
           <t>False</t>
@@ -5293,15 +5243,15 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
         <v>3</v>
       </c>
@@ -5350,7 +5300,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr">
         <is>
           <t>True</t>
@@ -5386,15 +5335,15 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
         <v>4</v>
       </c>
@@ -5443,7 +5392,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr">
         <is>
           <t>True</t>
@@ -5479,15 +5427,15 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
         <is>
           <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
         <v>1</v>
       </c>
@@ -5536,7 +5484,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr">
         <is>
           <t>False</t>
@@ -5572,15 +5519,15 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
         <v>3</v>
       </c>
@@ -5629,7 +5576,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr">
         <is>
           <t>True</t>
@@ -5665,15 +5611,15 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
         <v>3</v>
       </c>
@@ -5722,7 +5668,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr">
         <is>
           <t>True</t>
@@ -5758,15 +5703,15 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
         <v>3</v>
       </c>
@@ -5815,7 +5760,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr">
         <is>
           <t>False</t>
@@ -5851,15 +5795,15 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
         <v>2</v>
       </c>
@@ -5908,7 +5852,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr">
         <is>
           <t>True</t>
@@ -5944,15 +5887,15 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
         <is>
           <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
         <v>3</v>
       </c>
@@ -6001,7 +5944,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr">
         <is>
           <t>True</t>
@@ -6037,15 +5979,15 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
         <v>3</v>
       </c>
@@ -6094,7 +6036,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr">
         <is>
           <t>False</t>
@@ -6130,15 +6071,15 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
         <v>4</v>
       </c>
@@ -6188,7 +6129,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr">
         <is>
           <t>False</t>
@@ -6224,15 +6164,15 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
         <v>2</v>
       </c>
@@ -6281,7 +6221,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr">
         <is>
           <t>False</t>
@@ -6317,15 +6256,15 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
         <v>4</v>
       </c>
@@ -6374,7 +6313,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr">
         <is>
           <t>True</t>
@@ -6410,15 +6348,15 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
         <v>2</v>
       </c>
@@ -6467,7 +6405,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr">
         <is>
           <t>False</t>
@@ -6503,15 +6440,15 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
         <v>3</v>
       </c>
@@ -6560,7 +6497,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr">
         <is>
           <t>False</t>
@@ -6596,15 +6532,15 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
         <v>3</v>
       </c>
@@ -6694,15 +6630,15 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
         <v>2</v>
       </c>
@@ -6752,7 +6688,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr">
         <is>
           <t>True</t>
@@ -6788,15 +6723,15 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
         <v>4</v>
       </c>
@@ -6846,7 +6781,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R69" t="inlineStr"/>
       <c r="S69" t="inlineStr">
         <is>
           <t>False</t>
@@ -6882,15 +6816,15 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
         <v>3</v>
       </c>
@@ -6980,15 +6914,15 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
         <v>3</v>
       </c>
@@ -7078,15 +7012,15 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
         <v>3</v>
       </c>
@@ -7176,15 +7110,15 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
         <v>4</v>
       </c>
@@ -7274,15 +7208,15 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
         <v>3</v>
       </c>
@@ -7372,15 +7306,15 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
         <v>2</v>
       </c>
@@ -7430,7 +7364,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R75" t="inlineStr"/>
       <c r="S75" t="inlineStr">
         <is>
           <t>False</t>
@@ -7466,15 +7399,15 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
         <v>4</v>
       </c>
@@ -7524,7 +7457,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr">
         <is>
           <t>False</t>
@@ -7560,15 +7492,15 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達・加齢</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
         <is>
           <t>脳・神経</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
         <v>2</v>
       </c>
@@ -7617,7 +7549,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr">
         <is>
           <t>False</t>
@@ -7653,15 +7584,15 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達・加齢</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
         <is>
           <t>免疫機構</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
         <v>2</v>
       </c>
@@ -7710,7 +7641,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr">
         <is>
           <t>True</t>
@@ -7746,15 +7676,15 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達・加齢</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
         <is>
           <t>脳・神経</t>
         </is>
       </c>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
         <v>1</v>
       </c>
@@ -7803,7 +7733,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr">
         <is>
           <t>False</t>
@@ -7839,15 +7768,15 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
         <v>2</v>
       </c>
@@ -7896,7 +7825,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R80" t="inlineStr"/>
       <c r="S80" t="inlineStr">
         <is>
           <t>False</t>
@@ -7932,15 +7860,15 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
         <v>2</v>
       </c>
@@ -7989,7 +7917,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R81" t="inlineStr"/>
       <c r="S81" t="inlineStr">
         <is>
           <t>False</t>
@@ -8028,12 +7955,12 @@
           <t>疾病と障害の成り立ち及び回復過程の促進</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>病態の基礎</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
         <v>2</v>
       </c>
@@ -8082,7 +8009,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R82" t="inlineStr"/>
       <c r="S82" t="inlineStr">
         <is>
           <t>False</t>
@@ -8118,15 +8044,15 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
         <v>2</v>
       </c>
@@ -8175,7 +8101,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr">
         <is>
           <t>False</t>
@@ -8211,15 +8136,15 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
         <v>3</v>
       </c>
@@ -8268,7 +8193,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R84" t="inlineStr"/>
       <c r="S84" t="inlineStr">
         <is>
           <t>True</t>
@@ -8304,15 +8228,15 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>ロービジョン</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
         <is>
           <t>視能矯正訓練の対象となる視能障害</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
         <v>2</v>
       </c>
@@ -8361,7 +8285,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R85" t="inlineStr"/>
       <c r="S85" t="inlineStr">
         <is>
           <t>False</t>
@@ -8397,15 +8320,15 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
         <v>2</v>
       </c>
@@ -8454,7 +8377,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R86" t="inlineStr"/>
       <c r="S86" t="inlineStr">
         <is>
           <t>False</t>
@@ -8490,15 +8412,15 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
         <v>2</v>
       </c>
@@ -8547,7 +8469,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R87" t="inlineStr"/>
       <c r="S87" t="inlineStr">
         <is>
           <t>True</t>
@@ -8583,15 +8504,15 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
         <v>3</v>
       </c>
@@ -8640,7 +8561,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R88" t="inlineStr"/>
       <c r="S88" t="inlineStr">
         <is>
           <t>True</t>
@@ -8676,15 +8596,15 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
         <v>3</v>
       </c>
@@ -8733,7 +8653,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R89" t="inlineStr"/>
       <c r="S89" t="inlineStr">
         <is>
           <t>False</t>
@@ -8769,15 +8688,15 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
         <v>2</v>
       </c>
@@ -8826,7 +8745,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R90" t="inlineStr"/>
       <c r="S90" t="inlineStr">
         <is>
           <t>False</t>
@@ -8862,15 +8780,15 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
         <v>2</v>
       </c>
@@ -8919,7 +8837,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R91" t="inlineStr"/>
       <c r="S91" t="inlineStr">
         <is>
           <t>False</t>
@@ -8955,15 +8872,15 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
         <v>2</v>
       </c>
@@ -9012,7 +8929,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R92" t="inlineStr"/>
       <c r="S92" t="inlineStr">
         <is>
           <t>False</t>
@@ -9048,15 +8964,15 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G93" t="inlineStr"/>
       <c r="H93" t="n">
         <v>3</v>
       </c>
@@ -9106,7 +9022,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R93" t="inlineStr"/>
       <c r="S93" t="inlineStr">
         <is>
           <t>False</t>
@@ -9142,15 +9057,15 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
         <v>3</v>
       </c>
@@ -9199,7 +9114,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R94" t="inlineStr"/>
       <c r="S94" t="inlineStr">
         <is>
           <t>False</t>
@@ -9235,15 +9149,15 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
         <v>3</v>
       </c>
@@ -9292,7 +9206,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R95" t="inlineStr"/>
       <c r="S95" t="inlineStr">
         <is>
           <t>True</t>
@@ -9328,15 +9241,15 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
         <v>2</v>
       </c>
@@ -9385,7 +9298,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R96" t="inlineStr"/>
       <c r="S96" t="inlineStr">
         <is>
           <t>False</t>
@@ -9424,12 +9336,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr">
+      <c r="F97" t="inlineStr">
         <is>
           <t>視能訓練士の役割と義務</t>
         </is>
       </c>
+      <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
         <v>2</v>
       </c>
@@ -9478,7 +9390,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R97" t="inlineStr"/>
       <c r="S97" t="inlineStr">
         <is>
           <t>False</t>
@@ -9514,15 +9425,15 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
         <v>4</v>
       </c>
@@ -9571,7 +9482,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R98" t="inlineStr"/>
       <c r="S98" t="inlineStr">
         <is>
           <t>True</t>
@@ -9607,15 +9517,15 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
         <v>3</v>
       </c>
@@ -9705,15 +9615,15 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
         <v>2</v>
       </c>
@@ -9762,7 +9672,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R100" t="inlineStr"/>
       <c r="S100" t="inlineStr">
         <is>
           <t>False</t>
@@ -9798,15 +9707,15 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
         <v>3</v>
       </c>
@@ -9855,7 +9764,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R101" t="inlineStr"/>
       <c r="S101" t="inlineStr">
         <is>
           <t>False</t>
@@ -9891,15 +9799,15 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
         <v>3</v>
       </c>
@@ -9948,7 +9856,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R102" t="inlineStr"/>
       <c r="S102" t="inlineStr">
         <is>
           <t>False</t>
@@ -9984,15 +9891,15 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
         <v>3</v>
       </c>
@@ -10041,7 +9948,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R103" t="inlineStr"/>
       <c r="S103" t="inlineStr">
         <is>
           <t>True</t>
@@ -10077,15 +9983,15 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
         <v>2</v>
       </c>
@@ -10134,7 +10040,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R104" t="inlineStr"/>
       <c r="S104" t="inlineStr">
         <is>
           <t>True</t>
@@ -10170,15 +10075,15 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
         <v>2</v>
       </c>
@@ -10228,7 +10133,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R105" t="inlineStr"/>
       <c r="S105" t="inlineStr">
         <is>
           <t>False</t>
@@ -10264,15 +10168,15 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
         <v>3</v>
       </c>
@@ -10321,7 +10225,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R106" t="inlineStr"/>
       <c r="S106" t="inlineStr">
         <is>
           <t>False</t>
@@ -10357,15 +10260,15 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
         <v>2</v>
       </c>
@@ -10414,7 +10317,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R107" t="inlineStr"/>
       <c r="S107" t="inlineStr">
         <is>
           <t>False</t>
@@ -10450,15 +10352,15 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
         <v>1</v>
       </c>
@@ -10507,7 +10409,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R108" t="inlineStr"/>
       <c r="S108" t="inlineStr">
         <is>
           <t>False</t>
@@ -10543,15 +10444,15 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
         <v>2</v>
       </c>
@@ -10600,7 +10501,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R109" t="inlineStr"/>
       <c r="S109" t="inlineStr">
         <is>
           <t>False</t>
@@ -10636,15 +10536,15 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
         <v>2</v>
       </c>
@@ -10693,7 +10593,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R110" t="inlineStr"/>
       <c r="S110" t="inlineStr">
         <is>
           <t>False</t>
@@ -10729,15 +10628,15 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
         <v>2</v>
       </c>
@@ -10786,7 +10685,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R111" t="inlineStr"/>
       <c r="S111" t="inlineStr">
         <is>
           <t>False</t>
@@ -10822,15 +10720,15 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
         <v>2</v>
       </c>
@@ -10879,7 +10777,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R112" t="inlineStr"/>
       <c r="S112" t="inlineStr">
         <is>
           <t>False</t>
@@ -10915,15 +10812,15 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>眼科薬理学</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
         <is>
           <t>眼薬理学</t>
         </is>
       </c>
+      <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
         <v>2</v>
       </c>
@@ -10972,7 +10869,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R113" t="inlineStr"/>
       <c r="S113" t="inlineStr">
         <is>
           <t>True</t>
@@ -11008,15 +10904,15 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>眼科薬理学</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
         <is>
           <t>眼薬理学</t>
         </is>
       </c>
+      <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
         <v>2</v>
       </c>
@@ -11065,7 +10961,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R114" t="inlineStr"/>
       <c r="S114" t="inlineStr">
         <is>
           <t>False</t>
@@ -11101,15 +10996,15 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
         <v>2</v>
       </c>
@@ -11158,7 +11053,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R115" t="inlineStr"/>
       <c r="S115" t="inlineStr">
         <is>
           <t>False</t>
@@ -11194,15 +11088,15 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G116" t="inlineStr"/>
       <c r="H116" t="n">
         <v>1</v>
       </c>
@@ -11251,7 +11145,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R116" t="inlineStr"/>
       <c r="S116" t="inlineStr">
         <is>
           <t>False</t>
@@ -11287,15 +11180,15 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
         <v>2</v>
       </c>
@@ -11344,7 +11237,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R117" t="inlineStr"/>
       <c r="S117" t="inlineStr">
         <is>
           <t>False</t>
@@ -11380,15 +11272,15 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G118" t="inlineStr"/>
       <c r="H118" t="n">
         <v>2</v>
       </c>
@@ -11437,7 +11329,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R118" t="inlineStr"/>
       <c r="S118" t="inlineStr">
         <is>
           <t>False</t>
@@ -11473,15 +11364,15 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
         <v>3</v>
       </c>
@@ -11530,7 +11421,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R119" t="inlineStr"/>
       <c r="S119" t="inlineStr">
         <is>
           <t>True</t>
@@ -11566,15 +11456,15 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G120" t="inlineStr"/>
       <c r="H120" t="n">
         <v>1</v>
       </c>
@@ -11623,7 +11513,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R120" t="inlineStr"/>
       <c r="S120" t="inlineStr">
         <is>
           <t>False</t>
@@ -11659,15 +11548,15 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G121" t="inlineStr"/>
       <c r="H121" t="n">
         <v>3</v>
       </c>
@@ -11716,7 +11605,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R121" t="inlineStr"/>
       <c r="S121" t="inlineStr">
         <is>
           <t>True</t>
@@ -11752,15 +11640,15 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G122" t="inlineStr"/>
       <c r="H122" t="n">
         <v>1</v>
       </c>
@@ -11809,7 +11697,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R122" t="inlineStr"/>
       <c r="S122" t="inlineStr">
         <is>
           <t>False</t>
@@ -11845,15 +11732,15 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>眼科薬理学</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
         <is>
           <t>眼薬理学</t>
         </is>
       </c>
+      <c r="G123" t="inlineStr"/>
       <c r="H123" t="n">
         <v>3</v>
       </c>
@@ -11902,7 +11789,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R123" t="inlineStr"/>
       <c r="S123" t="inlineStr">
         <is>
           <t>True</t>
@@ -11938,15 +11824,15 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>ロービジョン</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
         <is>
           <t>視能矯正訓練の対象となる視能障害</t>
         </is>
       </c>
+      <c r="G124" t="inlineStr"/>
       <c r="H124" t="n">
         <v>3</v>
       </c>
@@ -11995,7 +11881,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R124" t="inlineStr"/>
       <c r="S124" t="inlineStr">
         <is>
           <t>False</t>
@@ -12031,15 +11916,15 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G125" t="inlineStr"/>
       <c r="H125" t="n">
         <v>2</v>
       </c>
@@ -12088,7 +11973,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R125" t="inlineStr"/>
       <c r="S125" t="inlineStr">
         <is>
           <t>False</t>
@@ -12124,15 +12008,15 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G126" t="inlineStr"/>
       <c r="H126" t="n">
         <v>4</v>
       </c>
@@ -12222,15 +12106,15 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr"/>
-      <c r="G127" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
         <v>3</v>
       </c>
@@ -12279,7 +12163,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R127" t="inlineStr"/>
       <c r="S127" t="inlineStr">
         <is>
           <t>False</t>
@@ -12315,15 +12198,15 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G128" t="inlineStr"/>
       <c r="H128" t="n">
         <v>2</v>
       </c>
@@ -12372,7 +12255,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R128" t="inlineStr"/>
       <c r="S128" t="inlineStr">
         <is>
           <t>False</t>
@@ -12408,15 +12290,15 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr"/>
-      <c r="G129" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G129" t="inlineStr"/>
       <c r="H129" t="n">
         <v>3</v>
       </c>
@@ -12466,7 +12348,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R129" t="inlineStr"/>
       <c r="S129" t="inlineStr">
         <is>
           <t>True</t>
@@ -12502,15 +12383,15 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>眼科薬理学</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
         <is>
           <t>眼薬理学</t>
         </is>
       </c>
+      <c r="G130" t="inlineStr"/>
       <c r="H130" t="n">
         <v>2</v>
       </c>
@@ -12559,7 +12440,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R130" t="inlineStr"/>
       <c r="S130" t="inlineStr">
         <is>
           <t>False</t>
@@ -12595,15 +12475,15 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>ロービジョン</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
         <is>
           <t>視能矯正訓練の対象となる視能障害</t>
         </is>
       </c>
+      <c r="G131" t="inlineStr"/>
       <c r="H131" t="n">
         <v>3</v>
       </c>
@@ -12652,7 +12532,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R131" t="inlineStr"/>
       <c r="S131" t="inlineStr">
         <is>
           <t>True</t>
@@ -12688,15 +12567,15 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr"/>
-      <c r="G132" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G132" t="inlineStr"/>
       <c r="H132" t="n">
         <v>2</v>
       </c>
@@ -12745,7 +12624,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R132" t="inlineStr"/>
       <c r="S132" t="inlineStr">
         <is>
           <t>False</t>
@@ -12781,15 +12659,15 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
         <is>
           <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
+      <c r="G133" t="inlineStr"/>
       <c r="H133" t="n">
         <v>3</v>
       </c>
@@ -12838,7 +12716,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R133" t="inlineStr"/>
       <c r="S133" t="inlineStr">
         <is>
           <t>True</t>
@@ -12874,15 +12751,15 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G134" t="inlineStr"/>
       <c r="H134" t="n">
         <v>2</v>
       </c>
@@ -12931,7 +12808,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R134" t="inlineStr"/>
       <c r="S134" t="inlineStr">
         <is>
           <t>False</t>
@@ -12967,15 +12843,15 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G135" t="inlineStr"/>
       <c r="H135" t="n">
         <v>4</v>
       </c>
@@ -13024,7 +12900,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R135" t="inlineStr"/>
       <c r="S135" t="inlineStr">
         <is>
           <t>False</t>
@@ -13060,15 +12935,15 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>ロービジョン</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
         <is>
           <t>視能矯正訓練の対象となる視能障害</t>
         </is>
       </c>
+      <c r="G136" t="inlineStr"/>
       <c r="H136" t="n">
         <v>2</v>
       </c>
@@ -13117,7 +12992,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R136" t="inlineStr"/>
       <c r="S136" t="inlineStr">
         <is>
           <t>True</t>
@@ -13153,15 +13027,15 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr"/>
-      <c r="G137" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G137" t="inlineStr"/>
       <c r="H137" t="n">
         <v>4</v>
       </c>
@@ -13210,7 +13084,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R137" t="inlineStr"/>
       <c r="S137" t="inlineStr">
         <is>
           <t>False</t>
@@ -13246,15 +13119,15 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr"/>
-      <c r="G138" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G138" t="inlineStr"/>
       <c r="H138" t="n">
         <v>3</v>
       </c>
@@ -13303,7 +13176,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R138" t="inlineStr"/>
       <c r="S138" t="inlineStr">
         <is>
           <t>False</t>
@@ -13339,15 +13211,15 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G139" t="inlineStr"/>
       <c r="H139" t="n">
         <v>4</v>
       </c>
@@ -13396,7 +13268,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R139" t="inlineStr"/>
       <c r="S139" t="inlineStr">
         <is>
           <t>True</t>
@@ -13432,15 +13303,15 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G140" t="inlineStr"/>
       <c r="H140" t="n">
         <v>3</v>
       </c>
@@ -13490,7 +13361,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R140" t="inlineStr"/>
       <c r="S140" t="inlineStr">
         <is>
           <t>False</t>
@@ -13526,15 +13396,15 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr"/>
-      <c r="G141" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G141" t="inlineStr"/>
       <c r="H141" t="n">
         <v>2</v>
       </c>
@@ -13583,7 +13453,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R141" t="inlineStr"/>
       <c r="S141" t="inlineStr">
         <is>
           <t>False</t>
@@ -13619,15 +13488,15 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr"/>
-      <c r="G142" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G142" t="inlineStr"/>
       <c r="H142" t="n">
         <v>2</v>
       </c>
@@ -13717,15 +13586,15 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr"/>
-      <c r="G143" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G143" t="inlineStr"/>
       <c r="H143" t="n">
         <v>1</v>
       </c>
@@ -13815,15 +13684,15 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G144" t="inlineStr"/>
       <c r="H144" t="n">
         <v>4</v>
       </c>
@@ -13873,7 +13742,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R144" t="inlineStr"/>
       <c r="S144" t="inlineStr">
         <is>
           <t>False</t>
@@ -13909,15 +13777,15 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G145" t="inlineStr"/>
       <c r="H145" t="n">
         <v>3</v>
       </c>
@@ -14007,15 +13875,15 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G146" t="inlineStr"/>
       <c r="H146" t="n">
         <v>4</v>
       </c>
@@ -14065,7 +13933,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R146" t="inlineStr"/>
       <c r="S146" t="inlineStr">
         <is>
           <t>False</t>
@@ -14101,15 +13968,15 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G147" t="inlineStr"/>
       <c r="H147" t="n">
         <v>2</v>
       </c>
@@ -14199,15 +14066,15 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G148" t="inlineStr"/>
       <c r="H148" t="n">
         <v>3</v>
       </c>
@@ -14297,15 +14164,15 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G149" t="inlineStr"/>
       <c r="H149" t="n">
         <v>3</v>
       </c>
@@ -14395,15 +14262,15 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G150" t="inlineStr"/>
       <c r="H150" t="n">
         <v>3</v>
       </c>
@@ -14493,15 +14360,15 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G151" t="inlineStr"/>
       <c r="H151" t="n">
         <v>3</v>
       </c>
@@ -14551,7 +14418,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R151" t="inlineStr"/>
       <c r="S151" t="inlineStr">
         <is>
           <t>False</t>

--- a/CO国試data/CO_questions_2016.xlsx
+++ b/CO国試data/CO_questions_2016.xlsx
@@ -542,12 +542,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>生殖、発生の概要</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>生殖、発生の概要</t>
+          <t>受精から個体発生</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -634,12 +634,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>遺伝</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>遺伝</t>
+          <t>遺伝子</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -726,12 +726,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>内分泌</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>内分泌</t>
+          <t>内分泌器官の構造と機能</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -818,12 +818,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>視能検査法と検査機器の基礎</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>視能検査法と検査機器の基礎</t>
+          <t>涙液検査</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -910,12 +910,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>視覚情報処理過程の概要</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>視覚情報処理過程の概要</t>
+          <t>瞳孔反応</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>心身の成長・発達、加齢</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>心身の成長・発達、加齢</t>
+          <t>新生児期、乳児期</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>視覚情報処理過程の概要</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>視覚情報処理過程の概要</t>
+          <t>眼窩</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1370,12 +1370,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>視覚情報処理過程の概要</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>視覚情報処理過程の概要</t>
+          <t>眼球</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1462,12 +1462,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1554,12 +1554,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>眼薬理学</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>眼薬理学</t>
+          <t>視能検査および視能矯正に用</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1646,12 +1646,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1738,12 +1738,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>生理光学の基礎知識</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1831,12 +1831,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -1923,12 +1923,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -2015,12 +2015,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -2107,12 +2107,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>生理光学の基礎知識</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -2199,12 +2199,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -2292,12 +2292,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>両眼視</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -2384,12 +2384,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>視能訓練士の役割と義務</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>視能訓練士の役割と義務</t>
+          <t>医療の質と安全の確保</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -2476,12 +2476,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -2568,12 +2568,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の対象となる視能障害</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>視能矯正訓練の対象となる視能障害</t>
+          <t>機能的視能障害</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -2660,12 +2660,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -2752,12 +2752,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -2845,12 +2845,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -2937,12 +2937,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -3029,12 +3029,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>前眼部、透光体検査</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -3213,12 +3213,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -3305,12 +3305,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>角膜検査</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -3397,12 +3397,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>眼圧検査</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>隅角検査</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>角膜検査</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -3673,12 +3673,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -3857,12 +3857,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>眼薬理学</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>眼薬理学</t>
+          <t>薬物の投与法</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -3949,12 +3949,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>公衆衛生学</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>公衆衛生学</t>
+          <t>公衆衛生総論</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -4041,12 +4041,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>輻湊、開散と屈折、調節</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -4139,12 +4139,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>眼瞼</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -4231,12 +4231,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>水晶体</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -4323,12 +4323,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>網膜</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -4415,12 +4415,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>角膜</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -4507,12 +4507,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
@@ -4691,12 +4691,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>調節異常</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -4783,12 +4783,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>全身疾患と眼</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
@@ -4875,12 +4875,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -4967,12 +4967,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>眼窩</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -5059,12 +5059,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -5151,12 +5151,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -5243,12 +5243,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
@@ -5335,12 +5335,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>視能矯正訓練の基本的知識</t>
+          <t>観血的視能矯正</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
@@ -5519,12 +5519,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
@@ -5611,12 +5611,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
@@ -5703,12 +5703,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -5795,12 +5795,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
@@ -5887,12 +5887,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>視能矯正訓練の基本的知識</t>
+          <t>光学的視能矯正</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
@@ -5979,12 +5979,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>後天眼球運動障害のリハビリ</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
@@ -6071,12 +6071,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
@@ -6164,12 +6164,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
@@ -6256,12 +6256,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
@@ -6348,12 +6348,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
@@ -6440,12 +6440,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -6532,12 +6532,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
@@ -6630,12 +6630,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -6723,12 +6723,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の矯正</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -6816,12 +6816,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
@@ -6914,12 +6914,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -7012,12 +7012,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>ぶどう膜</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -7110,12 +7110,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
@@ -7208,12 +7208,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
@@ -7306,12 +7306,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
@@ -7399,12 +7399,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>脳・神経</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>脳・神経</t>
+          <t>自律神経</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
@@ -7584,12 +7584,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>免疫機構</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>免疫機構</t>
+          <t>免疫系の構成・機能</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
@@ -7676,12 +7676,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>脳・神経</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>脳・神経</t>
+          <t>自律神経</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
@@ -7768,12 +7768,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
@@ -7860,12 +7860,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
@@ -7952,12 +7952,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>疾病と障害の成り立ち及び回復過程の促進</t>
+          <t>病態の基礎</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>病態の基礎</t>
+          <t>病因と疾病の種類</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
@@ -8044,12 +8044,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G83" t="inlineStr"/>
@@ -8136,12 +8136,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>身体症状症&lt;心因性視能障害&gt;</t>
         </is>
       </c>
       <c r="G84" t="inlineStr"/>
@@ -8228,12 +8228,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の対象となる視能障害</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>視能矯正訓練の対象となる視能障害</t>
+          <t>機能的視能障害</t>
         </is>
       </c>
       <c r="G85" t="inlineStr"/>
@@ -8320,12 +8320,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
@@ -8412,12 +8412,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
@@ -8504,12 +8504,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>輻湊、開散と屈折、調節</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
@@ -8596,12 +8596,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G89" t="inlineStr"/>
@@ -8688,12 +8688,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
@@ -8780,12 +8780,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G91" t="inlineStr"/>
@@ -8872,12 +8872,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G92" t="inlineStr"/>
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の矯正</t>
         </is>
       </c>
       <c r="G93" t="inlineStr"/>
@@ -9057,12 +9057,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G94" t="inlineStr"/>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G95" t="inlineStr"/>
@@ -9241,12 +9241,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G96" t="inlineStr"/>
@@ -9333,12 +9333,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>視能訓練士の役割と義務</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>視能訓練士の役割と義務</t>
+          <t>医療の質と安全の確保</t>
         </is>
       </c>
       <c r="G97" t="inlineStr"/>
@@ -9425,12 +9425,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>生理光学の基礎知識</t>
         </is>
       </c>
       <c r="G98" t="inlineStr"/>
@@ -9517,12 +9517,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G99" t="inlineStr"/>
@@ -9615,12 +9615,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G100" t="inlineStr"/>
@@ -9707,12 +9707,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G101" t="inlineStr"/>
@@ -9799,12 +9799,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>眼位と眼球運動</t>
         </is>
       </c>
       <c r="G102" t="inlineStr"/>
@@ -9891,12 +9891,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G103" t="inlineStr"/>
@@ -9983,12 +9983,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>前眼部、透光体検査</t>
         </is>
       </c>
       <c r="G104" t="inlineStr"/>
@@ -10075,12 +10075,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>角膜</t>
         </is>
       </c>
       <c r="G105" t="inlineStr"/>
@@ -10168,12 +10168,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G106" t="inlineStr"/>
@@ -10260,12 +10260,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>眼底検査</t>
         </is>
       </c>
       <c r="G107" t="inlineStr"/>
@@ -10352,12 +10352,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>眼圧検査</t>
         </is>
       </c>
       <c r="G108" t="inlineStr"/>
@@ -10444,12 +10444,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>涙液検査</t>
         </is>
       </c>
       <c r="G109" t="inlineStr"/>
@@ -10536,12 +10536,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G110" t="inlineStr"/>
@@ -10628,12 +10628,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G111" t="inlineStr"/>
@@ -10720,12 +10720,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G112" t="inlineStr"/>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>眼薬理学</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>眼薬理学</t>
+          <t>視能検査および視能矯正に用</t>
         </is>
       </c>
       <c r="G113" t="inlineStr"/>
@@ -10904,12 +10904,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>眼薬理学</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>眼薬理学</t>
+          <t>薬物の副作用</t>
         </is>
       </c>
       <c r="G114" t="inlineStr"/>
@@ -10996,12 +10996,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>定義</t>
         </is>
       </c>
       <c r="G115" t="inlineStr"/>
@@ -11088,12 +11088,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G116" t="inlineStr"/>
@@ -11180,12 +11180,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>緑内障</t>
         </is>
       </c>
       <c r="G117" t="inlineStr"/>
@@ -11272,12 +11272,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G118" t="inlineStr"/>
@@ -11364,12 +11364,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G119" t="inlineStr"/>
@@ -11456,12 +11456,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>網膜</t>
         </is>
       </c>
       <c r="G120" t="inlineStr"/>
@@ -11548,12 +11548,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G121" t="inlineStr"/>
@@ -11640,12 +11640,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G122" t="inlineStr"/>
@@ -11732,12 +11732,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>眼薬理学</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>眼薬理学</t>
+          <t>視能検査および視能矯正に用</t>
         </is>
       </c>
       <c r="G123" t="inlineStr"/>
@@ -11824,12 +11824,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の対象となる視能障害</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>視能矯正訓練の対象となる視能障害</t>
+          <t>機能的視能障害</t>
         </is>
       </c>
       <c r="G124" t="inlineStr"/>
@@ -11916,12 +11916,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G125" t="inlineStr"/>
@@ -12008,12 +12008,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G126" t="inlineStr"/>
@@ -12106,12 +12106,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G127" t="inlineStr"/>
@@ -12198,12 +12198,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G128" t="inlineStr"/>
@@ -12290,12 +12290,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G129" t="inlineStr"/>
@@ -12383,12 +12383,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>眼薬理学</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>眼薬理学</t>
+          <t>視能検査および視能矯正に用</t>
         </is>
       </c>
       <c r="G130" t="inlineStr"/>
@@ -12475,12 +12475,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の対象となる視能障害</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>視能矯正訓練の対象となる視能障害</t>
+          <t>機能的視能障害</t>
         </is>
       </c>
       <c r="G131" t="inlineStr"/>
@@ -12567,12 +12567,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G132" t="inlineStr"/>
@@ -12659,12 +12659,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>視能矯正訓練の基本的知識</t>
+          <t>観血的視能矯正</t>
         </is>
       </c>
       <c r="G133" t="inlineStr"/>
@@ -12751,12 +12751,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G134" t="inlineStr"/>
@@ -12843,12 +12843,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
       <c r="G135" t="inlineStr"/>
@@ -12935,12 +12935,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の対象となる視能障害</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>視能矯正訓練の対象となる視能障害</t>
+          <t>機能的視能障害</t>
         </is>
       </c>
       <c r="G136" t="inlineStr"/>
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G137" t="inlineStr"/>
@@ -13119,12 +13119,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G138" t="inlineStr"/>
@@ -13211,12 +13211,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>定義</t>
         </is>
       </c>
       <c r="G139" t="inlineStr"/>
@@ -13303,12 +13303,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G140" t="inlineStr"/>
@@ -13396,12 +13396,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G141" t="inlineStr"/>
@@ -13488,12 +13488,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G142" t="inlineStr"/>
@@ -13586,12 +13586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>眼瞼</t>
         </is>
       </c>
       <c r="G143" t="inlineStr"/>
@@ -13684,12 +13684,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の矯正</t>
         </is>
       </c>
       <c r="G144" t="inlineStr"/>
@@ -13777,12 +13777,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G145" t="inlineStr"/>
@@ -13875,12 +13875,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G146" t="inlineStr"/>
@@ -13968,12 +13968,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G147" t="inlineStr"/>
@@ -14066,12 +14066,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G148" t="inlineStr"/>
@@ -14164,12 +14164,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G149" t="inlineStr"/>
@@ -14262,12 +14262,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>水晶体</t>
         </is>
       </c>
       <c r="G150" t="inlineStr"/>
@@ -14360,12 +14360,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G151" t="inlineStr"/>

--- a/CO国試data/CO_questions_2016.xlsx
+++ b/CO国試data/CO_questions_2016.xlsx
@@ -550,7 +550,11 @@
           <t>受精から個体発生</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>眼の発生</t>
+        </is>
+      </c>
       <c r="H2" t="n">
         <v>2</v>
       </c>
@@ -642,7 +646,11 @@
           <t>遺伝子</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>基本構造と機能</t>
+        </is>
+      </c>
       <c r="H3" t="n">
         <v>1</v>
       </c>
@@ -734,7 +742,11 @@
           <t>内分泌器官の構造と機能</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>松果体</t>
+        </is>
+      </c>
       <c r="H4" t="n">
         <v>2</v>
       </c>
@@ -826,7 +838,6 @@
           <t>涙液検査</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>3</v>
       </c>
@@ -918,7 +929,11 @@
           <t>瞳孔反応</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>対光反射</t>
+        </is>
+      </c>
       <c r="H6" t="n">
         <v>2</v>
       </c>
@@ -1010,7 +1025,11 @@
           <t>新生児期、乳児期</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>新生児、乳児の生理</t>
+        </is>
+      </c>
       <c r="H7" t="n">
         <v>2</v>
       </c>
@@ -1102,7 +1121,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>2</v>
       </c>
@@ -1194,7 +1212,11 @@
           <t>眼窩</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>視神経管</t>
+        </is>
+      </c>
       <c r="H9" t="n">
         <v>2</v>
       </c>
@@ -1286,7 +1308,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>2</v>
       </c>
@@ -1378,7 +1399,11 @@
           <t>眼球</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ぶどう膜（虹彩、毛様体、脈絡膜）</t>
+        </is>
+      </c>
       <c r="H11" t="n">
         <v>1</v>
       </c>
@@ -1470,7 +1495,11 @@
           <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>外眼筋の単独作用</t>
+        </is>
+      </c>
       <c r="H12" t="n">
         <v>3</v>
       </c>
@@ -1562,7 +1591,11 @@
           <t>視能検査および視能矯正に用</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>局所麻酔薬</t>
+        </is>
+      </c>
       <c r="H13" t="n">
         <v>2</v>
       </c>
@@ -1654,7 +1687,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>麻痺性斜視</t>
+        </is>
+      </c>
       <c r="H14" t="n">
         <v>2</v>
       </c>
@@ -1746,7 +1783,11 @@
           <t>生理光学の基礎知識</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>レンズ</t>
+        </is>
+      </c>
       <c r="H15" t="n">
         <v>3</v>
       </c>
@@ -1839,7 +1880,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H16" t="n">
         <v>2</v>
       </c>
@@ -1931,7 +1976,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>視覚の閾値</t>
+        </is>
+      </c>
       <c r="H17" t="n">
         <v>3</v>
       </c>
@@ -2023,7 +2072,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>2</v>
       </c>
@@ -2115,7 +2163,11 @@
           <t>生理光学の基礎知識</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>プリズム</t>
+        </is>
+      </c>
       <c r="H19" t="n">
         <v>3</v>
       </c>
@@ -2207,7 +2259,11 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>遠視</t>
+        </is>
+      </c>
       <c r="H20" t="n">
         <v>3</v>
       </c>
@@ -2300,7 +2356,11 @@
           <t>両眼視</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>両眼視の成立条件</t>
+        </is>
+      </c>
       <c r="H21" t="n">
         <v>1</v>
       </c>
@@ -2392,7 +2452,6 @@
           <t>医療の質と安全の確保</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>2</v>
       </c>
@@ -2484,7 +2543,11 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>遠見、近見視力検査</t>
+        </is>
+      </c>
       <c r="H23" t="n">
         <v>2</v>
       </c>
@@ -2576,7 +2639,6 @@
           <t>機能的視能障害</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>4</v>
       </c>
@@ -2668,7 +2730,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>視覚の成り立ち</t>
+        </is>
+      </c>
       <c r="H25" t="n">
         <v>2</v>
       </c>
@@ -2760,7 +2826,11 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>遠視</t>
+        </is>
+      </c>
       <c r="H26" t="n">
         <v>4</v>
       </c>
@@ -2853,7 +2923,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>交代性上斜位</t>
+        </is>
+      </c>
       <c r="H27" t="n">
         <v>3</v>
       </c>
@@ -2945,7 +3019,11 @@
           <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>外眼筋の単独作用</t>
+        </is>
+      </c>
       <c r="H28" t="n">
         <v>3</v>
       </c>
@@ -3037,7 +3115,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
         <v>2</v>
       </c>
@@ -3129,7 +3206,11 @@
           <t>前眼部、透光体検査</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>細隙灯顕微鏡検査</t>
+        </is>
+      </c>
       <c r="H30" t="n">
         <v>2</v>
       </c>
@@ -3221,7 +3302,6 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
         <v>4</v>
       </c>
@@ -3313,7 +3393,11 @@
           <t>角膜検査</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>角膜内皮細胞検査</t>
+        </is>
+      </c>
       <c r="H32" t="n">
         <v>3</v>
       </c>
@@ -3405,7 +3489,6 @@
           <t>眼圧検査</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
         <v>2</v>
       </c>
@@ -3497,7 +3580,6 @@
           <t>隅角検査</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
         <v>2</v>
       </c>
@@ -3589,7 +3671,11 @@
           <t>角膜検査</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>角膜厚検査</t>
+        </is>
+      </c>
       <c r="H35" t="n">
         <v>2</v>
       </c>
@@ -3681,7 +3767,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>上下斜視</t>
+        </is>
+      </c>
       <c r="H36" t="n">
         <v>3</v>
       </c>
@@ -3773,7 +3863,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H37" t="n">
         <v>3</v>
       </c>
@@ -3865,7 +3959,11 @@
           <t>薬物の投与法</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>局所投与</t>
+        </is>
+      </c>
       <c r="H38" t="n">
         <v>3</v>
       </c>
@@ -3957,7 +4055,6 @@
           <t>公衆衛生総論</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
         <v>2</v>
       </c>
@@ -4049,7 +4146,11 @@
           <t>輻湊、開散と屈折、調節</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>定義</t>
+        </is>
+      </c>
       <c r="H40" t="n">
         <v>3</v>
       </c>
@@ -4147,7 +4248,11 @@
           <t>眼瞼</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>麦粒腫</t>
+        </is>
+      </c>
       <c r="H41" t="n">
         <v>1</v>
       </c>
@@ -4239,7 +4344,11 @@
           <t>水晶体</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>水晶体偏位、脱臼</t>
+        </is>
+      </c>
       <c r="H42" t="n">
         <v>2</v>
       </c>
@@ -4331,7 +4440,11 @@
           <t>網膜</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>網膜色素変性、その他の変性およびジストロフィ</t>
+        </is>
+      </c>
       <c r="H43" t="n">
         <v>2</v>
       </c>
@@ -4423,7 +4536,11 @@
           <t>角膜</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>角膜変性（症）、角膜ジストロフィ</t>
+        </is>
+      </c>
       <c r="H44" t="n">
         <v>2</v>
       </c>
@@ -4515,7 +4632,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
         <v>2</v>
       </c>
@@ -4607,7 +4723,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
         <v>3</v>
       </c>
@@ -4699,7 +4814,6 @@
           <t>調節異常</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
         <v>3</v>
       </c>
@@ -4791,7 +4905,6 @@
           <t>全身疾患と眼</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
         <v>2</v>
       </c>
@@ -4883,7 +4996,11 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>うっ血乳頭</t>
+        </is>
+      </c>
       <c r="H49" t="n">
         <v>2</v>
       </c>
@@ -4975,7 +5092,11 @@
           <t>眼窩</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>眼球突出、陥凹</t>
+        </is>
+      </c>
       <c r="H50" t="n">
         <v>1</v>
       </c>
@@ -5067,7 +5188,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H51" t="n">
         <v>4</v>
       </c>
@@ -5159,7 +5284,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>外斜視</t>
+        </is>
+      </c>
       <c r="H52" t="n">
         <v>3</v>
       </c>
@@ -5251,7 +5380,6 @@
           <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
         <v>3</v>
       </c>
@@ -5343,7 +5471,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>微小斜視</t>
+        </is>
+      </c>
       <c r="H54" t="n">
         <v>4</v>
       </c>
@@ -5435,7 +5567,11 @@
           <t>観血的視能矯正</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>適応と方法</t>
+        </is>
+      </c>
       <c r="H55" t="n">
         <v>1</v>
       </c>
@@ -5527,7 +5663,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>形態覚遮断弱視</t>
+        </is>
+      </c>
       <c r="H56" t="n">
         <v>3</v>
       </c>
@@ -5619,7 +5759,6 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
         <v>3</v>
       </c>
@@ -5711,7 +5850,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>不同視弱視</t>
+        </is>
+      </c>
       <c r="H58" t="n">
         <v>3</v>
       </c>
@@ -5803,7 +5946,11 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>屈折矯正</t>
+        </is>
+      </c>
       <c r="H59" t="n">
         <v>2</v>
       </c>
@@ -5895,7 +6042,11 @@
           <t>光学的視能矯正</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>プリズム</t>
+        </is>
+      </c>
       <c r="H60" t="n">
         <v>3</v>
       </c>
@@ -5987,7 +6138,11 @@
           <t>後天眼球運動障害のリハビリ</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>眼球運動訓練</t>
+        </is>
+      </c>
       <c r="H61" t="n">
         <v>3</v>
       </c>
@@ -6079,7 +6234,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
         <v>4</v>
       </c>
@@ -6172,7 +6326,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>不同視弱視</t>
+        </is>
+      </c>
       <c r="H63" t="n">
         <v>2</v>
       </c>
@@ -6264,7 +6422,6 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
         <v>4</v>
       </c>
@@ -6356,7 +6513,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
         <v>2</v>
       </c>
@@ -6448,7 +6604,11 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>遮閉法</t>
+        </is>
+      </c>
       <c r="H66" t="n">
         <v>3</v>
       </c>
@@ -6540,7 +6700,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
         <v>3</v>
       </c>
@@ -6638,7 +6797,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
         <v>2</v>
       </c>
@@ -6731,7 +6889,11 @@
           <t>屈折、調節の矯正</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>眼鏡レンズ</t>
+        </is>
+      </c>
       <c r="H69" t="n">
         <v>4</v>
       </c>
@@ -6824,7 +6986,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H70" t="n">
         <v>3</v>
       </c>
@@ -6922,7 +7088,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>外斜視</t>
+        </is>
+      </c>
       <c r="H71" t="n">
         <v>3</v>
       </c>
@@ -7020,7 +7190,11 @@
           <t>ぶどう膜</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>ぶどう膜炎</t>
+        </is>
+      </c>
       <c r="H72" t="n">
         <v>3</v>
       </c>
@@ -7118,7 +7292,11 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>視交叉から後頭葉までの視覚伝導路の疾患</t>
+        </is>
+      </c>
       <c r="H73" t="n">
         <v>4</v>
       </c>
@@ -7216,7 +7394,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>交代性上斜位</t>
+        </is>
+      </c>
       <c r="H74" t="n">
         <v>3</v>
       </c>
@@ -7314,7 +7496,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H75" t="n">
         <v>2</v>
       </c>
@@ -7407,7 +7593,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
         <v>4</v>
       </c>
@@ -7500,7 +7685,11 @@
           <t>自律神経</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>副交感神経</t>
+        </is>
+      </c>
       <c r="H77" t="n">
         <v>2</v>
       </c>
@@ -7592,7 +7781,6 @@
           <t>免疫系の構成・機能</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
         <v>2</v>
       </c>
@@ -7684,7 +7872,11 @@
           <t>自律神経</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>副交感神経</t>
+        </is>
+      </c>
       <c r="H79" t="n">
         <v>1</v>
       </c>
@@ -7776,7 +7968,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
         <v>2</v>
       </c>
@@ -7868,7 +8059,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
         <v>2</v>
       </c>
@@ -7960,7 +8150,11 @@
           <t>病因と疾病の種類</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>染色体、遺伝子異常</t>
+        </is>
+      </c>
       <c r="H82" t="n">
         <v>2</v>
       </c>
@@ -8052,7 +8246,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
         <v>2</v>
       </c>
@@ -8144,7 +8337,6 @@
           <t>身体症状症&lt;心因性視能障害&gt;</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
         <v>3</v>
       </c>
@@ -8236,7 +8428,6 @@
           <t>機能的視能障害</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
         <v>2</v>
       </c>
@@ -8328,7 +8519,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
         <v>2</v>
       </c>
@@ -8420,7 +8610,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
         <v>2</v>
       </c>
@@ -8512,7 +8701,11 @@
           <t>輻湊、開散と屈折、調節</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>測定法</t>
+        </is>
+      </c>
       <c r="H88" t="n">
         <v>3</v>
       </c>
@@ -8604,7 +8797,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
         <v>3</v>
       </c>
@@ -8696,7 +8888,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H90" t="n">
         <v>2</v>
       </c>
@@ -8788,7 +8984,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
         <v>2</v>
       </c>
@@ -8880,7 +9075,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
         <v>2</v>
       </c>
@@ -8972,7 +9166,11 @@
           <t>屈折、調節の矯正</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>コンタクトレンズ</t>
+        </is>
+      </c>
       <c r="H93" t="n">
         <v>3</v>
       </c>
@@ -9065,7 +9263,11 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>乱視</t>
+        </is>
+      </c>
       <c r="H94" t="n">
         <v>3</v>
       </c>
@@ -9157,7 +9359,6 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
         <v>3</v>
       </c>
@@ -9249,7 +9450,11 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>視交叉から後頭葉までの視覚伝導路の疾患</t>
+        </is>
+      </c>
       <c r="H96" t="n">
         <v>2</v>
       </c>
@@ -9341,7 +9546,6 @@
           <t>医療の質と安全の確保</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
         <v>2</v>
       </c>
@@ -9433,7 +9637,11 @@
           <t>生理光学の基礎知識</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>レンズ</t>
+        </is>
+      </c>
       <c r="H98" t="n">
         <v>4</v>
       </c>
@@ -9525,7 +9733,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H99" t="n">
         <v>3</v>
       </c>
@@ -9623,7 +9835,6 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
         <v>2</v>
       </c>
@@ -9715,7 +9926,6 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
         <v>3</v>
       </c>
@@ -9807,7 +10017,6 @@
           <t>眼位と眼球運動</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
         <v>3</v>
       </c>
@@ -9899,7 +10108,6 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
         <v>3</v>
       </c>
@@ -9991,7 +10199,11 @@
           <t>前眼部、透光体検査</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>細隙灯顕微鏡検査</t>
+        </is>
+      </c>
       <c r="H104" t="n">
         <v>2</v>
       </c>
@@ -10083,7 +10295,6 @@
           <t>角膜</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
         <v>2</v>
       </c>
@@ -10176,7 +10387,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H106" t="n">
         <v>3</v>
       </c>
@@ -10268,7 +10483,11 @@
           <t>眼底検査</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>前置レンズ検査</t>
+        </is>
+      </c>
       <c r="H107" t="n">
         <v>2</v>
       </c>
@@ -10360,7 +10579,6 @@
           <t>眼圧検査</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
         <v>1</v>
       </c>
@@ -10452,7 +10670,11 @@
           <t>涙液検査</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Schirmer試験</t>
+        </is>
+      </c>
       <c r="H109" t="n">
         <v>2</v>
       </c>
@@ -10544,7 +10766,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
         <v>2</v>
       </c>
@@ -10636,7 +10857,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H111" t="n">
         <v>2</v>
       </c>
@@ -10728,7 +10953,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr"/>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H112" t="n">
         <v>2</v>
       </c>
@@ -10820,7 +11049,11 @@
           <t>視能検査および視能矯正に用</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>局所麻酔薬</t>
+        </is>
+      </c>
       <c r="H113" t="n">
         <v>2</v>
       </c>
@@ -10912,7 +11145,11 @@
           <t>薬物の副作用</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>眼科で用いられる薬物の副作用</t>
+        </is>
+      </c>
       <c r="H114" t="n">
         <v>2</v>
       </c>
@@ -11004,7 +11241,6 @@
           <t>定義</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
         <v>2</v>
       </c>
@@ -11096,7 +11332,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr"/>
       <c r="H116" t="n">
         <v>1</v>
       </c>
@@ -11188,7 +11423,11 @@
           <t>緑内障</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>正常眼圧緑内障</t>
+        </is>
+      </c>
       <c r="H117" t="n">
         <v>2</v>
       </c>
@@ -11280,7 +11519,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr"/>
       <c r="H118" t="n">
         <v>2</v>
       </c>
@@ -11372,7 +11610,11 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>うっ血乳頭</t>
+        </is>
+      </c>
       <c r="H119" t="n">
         <v>3</v>
       </c>
@@ -11464,7 +11706,11 @@
           <t>網膜</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>網膜色素変性、その他の変性およびジストロフィ</t>
+        </is>
+      </c>
       <c r="H120" t="n">
         <v>1</v>
       </c>
@@ -11556,7 +11802,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr"/>
       <c r="H121" t="n">
         <v>3</v>
       </c>
@@ -11648,7 +11893,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr"/>
       <c r="H122" t="n">
         <v>1</v>
       </c>
@@ -11740,7 +11984,6 @@
           <t>視能検査および視能矯正に用</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr"/>
       <c r="H123" t="n">
         <v>3</v>
       </c>
@@ -11832,7 +12075,6 @@
           <t>機能的視能障害</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr"/>
       <c r="H124" t="n">
         <v>3</v>
       </c>
@@ -11924,7 +12166,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>麻痺性斜視</t>
+        </is>
+      </c>
       <c r="H125" t="n">
         <v>2</v>
       </c>
@@ -12016,7 +12262,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr"/>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>外斜視</t>
+        </is>
+      </c>
       <c r="H126" t="n">
         <v>4</v>
       </c>
@@ -12114,7 +12364,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
         <v>3</v>
       </c>
@@ -12206,7 +12455,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr"/>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>形態覚遮断弱視</t>
+        </is>
+      </c>
       <c r="H128" t="n">
         <v>2</v>
       </c>
@@ -12298,7 +12551,6 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr"/>
       <c r="H129" t="n">
         <v>3</v>
       </c>
@@ -12391,7 +12643,11 @@
           <t>視能検査および視能矯正に用</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>副交感神経薬</t>
+        </is>
+      </c>
       <c r="H130" t="n">
         <v>2</v>
       </c>
@@ -12483,7 +12739,6 @@
           <t>機能的視能障害</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr"/>
       <c r="H131" t="n">
         <v>3</v>
       </c>
@@ -12575,7 +12830,6 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr"/>
       <c r="H132" t="n">
         <v>2</v>
       </c>
@@ -12667,7 +12921,11 @@
           <t>観血的視能矯正</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr"/>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>合併症</t>
+        </is>
+      </c>
       <c r="H133" t="n">
         <v>3</v>
       </c>
@@ -12759,7 +13017,6 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr"/>
       <c r="H134" t="n">
         <v>2</v>
       </c>
@@ -12851,7 +13108,11 @@
           <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr"/>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>外眼筋の単独作用</t>
+        </is>
+      </c>
       <c r="H135" t="n">
         <v>4</v>
       </c>
@@ -12943,7 +13204,6 @@
           <t>機能的視能障害</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr"/>
       <c r="H136" t="n">
         <v>2</v>
       </c>
@@ -13035,7 +13295,6 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr"/>
       <c r="H137" t="n">
         <v>4</v>
       </c>
@@ -13127,7 +13386,6 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr"/>
       <c r="H138" t="n">
         <v>3</v>
       </c>
@@ -13219,7 +13477,6 @@
           <t>定義</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr"/>
       <c r="H139" t="n">
         <v>4</v>
       </c>
@@ -13311,7 +13568,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr"/>
       <c r="H140" t="n">
         <v>3</v>
       </c>
@@ -13404,7 +13660,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>交代性上斜位</t>
+        </is>
+      </c>
       <c r="H141" t="n">
         <v>2</v>
       </c>
@@ -13496,7 +13756,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr"/>
       <c r="H142" t="n">
         <v>2</v>
       </c>
@@ -13594,7 +13853,6 @@
           <t>眼瞼</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr"/>
       <c r="H143" t="n">
         <v>1</v>
       </c>
@@ -13692,7 +13950,11 @@
           <t>屈折、調節の矯正</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>眼鏡レンズ</t>
+        </is>
+      </c>
       <c r="H144" t="n">
         <v>4</v>
       </c>
@@ -13785,7 +14047,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>上下斜視</t>
+        </is>
+      </c>
       <c r="H145" t="n">
         <v>3</v>
       </c>
@@ -13883,7 +14149,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H146" t="n">
         <v>4</v>
       </c>
@@ -13976,7 +14246,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr"/>
       <c r="H147" t="n">
         <v>2</v>
       </c>
@@ -14074,7 +14343,6 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr"/>
       <c r="H148" t="n">
         <v>3</v>
       </c>
@@ -14172,7 +14440,6 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr"/>
       <c r="H149" t="n">
         <v>3</v>
       </c>
@@ -14270,7 +14537,11 @@
           <t>水晶体</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>白内障</t>
+        </is>
+      </c>
       <c r="H150" t="n">
         <v>3</v>
       </c>
@@ -14368,7 +14639,11 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>屈折矯正</t>
+        </is>
+      </c>
       <c r="H151" t="n">
         <v>3</v>
       </c>

--- a/CO国試data/CO_questions_2016.xlsx
+++ b/CO国試data/CO_questions_2016.xlsx
@@ -603,10 +603,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S2" t="b">
+        <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -699,10 +697,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S3" t="b">
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,10 +882,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S5" t="b">
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -982,10 +976,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S6" t="b">
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1078,10 +1070,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S7" t="b">
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1169,10 +1159,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S8" t="b">
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1356,10 +1344,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S10" t="b">
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1452,10 +1438,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S11" t="b">
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1548,10 +1532,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S12" t="b">
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1644,10 +1626,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S13" t="b">
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1740,10 +1720,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S14" t="b">
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1837,10 +1815,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S15" t="b">
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1933,10 +1909,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S16" t="b">
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2029,10 +2003,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S17" t="b">
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2120,10 +2092,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S18" t="b">
+        <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2216,10 +2186,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S19" t="b">
+        <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2313,10 +2281,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S20" t="b">
+        <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2409,10 +2375,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S21" t="b">
+        <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2500,10 +2464,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S22" t="b">
+        <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2596,10 +2558,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S23" t="b">
+        <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2687,10 +2647,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S24" t="b">
+        <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2783,10 +2741,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S25" t="b">
+        <v>0</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2880,10 +2836,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S26" t="b">
+        <v>0</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -2976,10 +2930,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S27" t="b">
+        <v>0</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3072,10 +3024,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S28" t="b">
+        <v>0</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3163,10 +3113,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S29" t="b">
+        <v>0</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3259,10 +3207,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S30" t="b">
+        <v>0</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3350,10 +3296,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S31" t="b">
+        <v>0</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3446,10 +3390,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S32" t="b">
+        <v>0</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3537,10 +3479,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S33" t="b">
+        <v>0</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3628,10 +3568,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S34" t="b">
+        <v>0</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3724,10 +3662,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S35" t="b">
+        <v>0</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3820,10 +3756,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S36" t="b">
+        <v>0</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -3916,10 +3850,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S37" t="b">
+        <v>0</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4012,10 +3944,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S38" t="b">
+        <v>0</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4205,10 +4135,8 @@
           <t>2016_co_16_am039.jpg</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S40" t="b">
+        <v>0</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4301,10 +4229,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S41" t="b">
+        <v>0</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4397,10 +4323,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S42" t="b">
+        <v>0</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4493,10 +4417,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S43" t="b">
+        <v>0</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4680,10 +4602,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S45" t="b">
+        <v>0</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4953,10 +4873,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S48" t="b">
+        <v>0</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5049,10 +4967,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S49" t="b">
+        <v>0</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5145,10 +5061,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S50" t="b">
+        <v>0</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5241,10 +5155,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S51" t="b">
+        <v>0</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5337,10 +5249,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S52" t="b">
+        <v>0</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5620,10 +5530,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S55" t="b">
+        <v>0</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5807,10 +5715,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S57" t="b">
+        <v>0</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -5903,10 +5809,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S58" t="b">
+        <v>0</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6095,10 +5999,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S60" t="b">
+        <v>0</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6191,10 +6093,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S61" t="b">
+        <v>0</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6283,10 +6183,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S62" t="b">
+        <v>0</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6379,10 +6277,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S63" t="b">
+        <v>0</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6561,10 +6457,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S65" t="b">
+        <v>0</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -6657,10 +6551,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S66" t="b">
+        <v>0</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -6754,10 +6646,8 @@
           <t>2016_co_16_am066.jpg</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S67" t="b">
+        <v>0</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -6943,10 +6833,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S69" t="b">
+        <v>0</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7249,10 +7137,8 @@
           <t>2016_co_16_am071.jpg</t>
         </is>
       </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S72" t="b">
+        <v>0</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7351,10 +7237,8 @@
           <t>2016_co_16_am072.jpg</t>
         </is>
       </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S73" t="b">
+        <v>0</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7453,10 +7337,8 @@
           <t>2016_co_16_am073.jpg</t>
         </is>
       </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S74" t="b">
+        <v>0</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7550,10 +7432,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S75" t="b">
+        <v>0</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -7642,10 +7522,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S76" t="b">
+        <v>0</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -7738,10 +7616,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S77" t="b">
+        <v>0</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -7925,10 +7801,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S79" t="b">
+        <v>0</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8016,10 +7890,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S80" t="b">
+        <v>0</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8107,10 +7979,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S81" t="b">
+        <v>0</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8203,10 +8073,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S82" t="b">
+        <v>0</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8294,10 +8162,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S83" t="b">
+        <v>0</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8476,10 +8342,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S85" t="b">
+        <v>0</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -8567,10 +8431,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S86" t="b">
+        <v>0</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -8658,10 +8520,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S87" t="b">
+        <v>0</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -8845,10 +8705,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S89" t="b">
+        <v>0</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -8941,10 +8799,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S90" t="b">
+        <v>0</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9032,10 +8888,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S91" t="b">
+        <v>0</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9123,10 +8977,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S92" t="b">
+        <v>0</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -9220,10 +9072,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S93" t="b">
+        <v>0</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -9316,10 +9166,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S94" t="b">
+        <v>0</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -9503,10 +9351,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S96" t="b">
+        <v>0</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -9594,10 +9440,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S97" t="b">
+        <v>0</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -9792,10 +9636,8 @@
           <t>2016_co_16_pm023.jpg</t>
         </is>
       </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S99" t="b">
+        <v>0</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -9883,10 +9725,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S100" t="b">
+        <v>0</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -9974,10 +9814,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S101" t="b">
+        <v>0</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10065,10 +9903,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S102" t="b">
+        <v>0</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -10344,10 +10180,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S105" t="b">
+        <v>0</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -10440,10 +10274,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S106" t="b">
+        <v>0</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -10536,10 +10368,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S107" t="b">
+        <v>0</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -10627,10 +10457,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S108" t="b">
+        <v>0</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -10723,10 +10551,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S109" t="b">
+        <v>0</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -10814,10 +10640,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S110" t="b">
+        <v>0</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -10910,10 +10734,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S111" t="b">
+        <v>0</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -11006,10 +10828,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S112" t="b">
+        <v>0</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -11198,10 +11018,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S114" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S114" t="b">
+        <v>0</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -11289,10 +11107,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S115" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S115" t="b">
+        <v>0</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -11380,10 +11196,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S116" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S116" t="b">
+        <v>0</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -11476,10 +11290,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S117" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S117" t="b">
+        <v>0</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -11567,10 +11379,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S118" t="b">
+        <v>0</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -11759,10 +11569,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S120" t="b">
+        <v>0</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -11941,10 +11749,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S122" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S122" t="b">
+        <v>0</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -12032,10 +11838,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S123" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S123" t="b">
+        <v>0</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -12123,10 +11927,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S124" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S124" t="b">
+        <v>0</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -12219,10 +12021,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S125" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S125" t="b">
+        <v>0</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -12321,10 +12121,8 @@
           <t>2016_co_16_pm050.jpg</t>
         </is>
       </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S126" t="b">
+        <v>0</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -12412,10 +12210,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S127" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S127" t="b">
+        <v>0</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -12508,10 +12304,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S128" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S128" t="b">
+        <v>0</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -12696,10 +12490,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S130" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S130" t="b">
+        <v>0</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -12878,10 +12670,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S132" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S132" t="b">
+        <v>0</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -13065,10 +12855,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S134" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S134" t="b">
+        <v>0</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -13161,10 +12949,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S135" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S135" t="b">
+        <v>0</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -13252,10 +13038,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S136" t="b">
+        <v>0</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -13343,10 +13127,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S137" t="b">
+        <v>0</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -13434,10 +13216,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S138" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S138" t="b">
+        <v>0</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -13617,10 +13397,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S140" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S140" t="b">
+        <v>0</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -13713,10 +13491,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S141" t="b">
+        <v>0</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -13810,10 +13586,8 @@
           <t>2016_co_16_pm066.jpg</t>
         </is>
       </c>
-      <c r="S142" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S142" t="b">
+        <v>0</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -13907,10 +13681,8 @@
           <t>2016_co_16_pm067.jpg</t>
         </is>
       </c>
-      <c r="S143" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S143" t="b">
+        <v>0</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -14004,10 +13776,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S144" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S144" t="b">
+        <v>0</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -14106,10 +13876,8 @@
           <t>2016_co_16_pm069.jpg</t>
         </is>
       </c>
-      <c r="S145" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S145" t="b">
+        <v>0</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -14203,10 +13971,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S146" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S146" t="b">
+        <v>0</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -14300,10 +14066,8 @@
           <t>2016_co_16_pm071.jpg</t>
         </is>
       </c>
-      <c r="S147" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S147" t="b">
+        <v>0</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -14397,10 +14161,8 @@
           <t>2016_co_16_pm072.jpg</t>
         </is>
       </c>
-      <c r="S148" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S148" t="b">
+        <v>0</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -14596,10 +14358,8 @@
           <t>2016_co_16_pm074.jpg</t>
         </is>
       </c>
-      <c r="S150" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S150" t="b">
+        <v>0</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -14693,10 +14453,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S151" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S151" t="b">
+        <v>0</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>

--- a/CO国試data/CO_questions_2016.xlsx
+++ b/CO国試data/CO_questions_2016.xlsx
@@ -778,7 +778,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -791,10 +791,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S4" t="b">
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1240,7 +1238,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>BD</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1253,10 +1251,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S9" t="b">
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -4020,7 +4016,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>BC</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4033,10 +4029,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S39" t="b">
+        <v>1</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4498,7 +4492,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -4511,10 +4505,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S44" t="b">
+        <v>1</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4678,7 +4670,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -4691,10 +4683,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S46" t="b">
+        <v>1</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -4769,7 +4759,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -4782,10 +4772,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S47" t="b">
+        <v>1</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5325,7 +5313,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -5338,10 +5326,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S53" t="b">
+        <v>1</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5421,7 +5407,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -5434,10 +5420,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S54" t="b">
+        <v>1</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5611,7 +5595,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -5624,10 +5608,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S56" t="b">
+        <v>1</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -5890,7 +5872,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -5903,10 +5885,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S59" t="b">
+        <v>1</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6264,7 +6244,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -6278,7 +6258,7 @@
         </is>
       </c>
       <c r="S63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6353,7 +6333,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -6366,10 +6346,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S64" t="b">
+        <v>1</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6723,7 +6701,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>BD</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -6736,10 +6714,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S68" t="b">
+        <v>1</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -6915,7 +6891,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -6933,10 +6909,8 @@
           <t>2016_co_16_am069.jpg</t>
         </is>
       </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S70" t="b">
+        <v>1</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7017,7 +6991,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>BC</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -7035,10 +7009,8 @@
           <t>2016_co_16_am070.jpg</t>
         </is>
       </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S71" t="b">
+        <v>1</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7692,7 +7664,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -7705,10 +7677,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S78" t="b">
+        <v>1</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8238,7 +8208,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -8251,10 +8221,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S84" t="b">
+        <v>1</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8601,7 +8569,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -8614,10 +8582,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S88" t="b">
+        <v>1</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9242,7 +9208,7 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -9255,10 +9221,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S95" t="b">
+        <v>1</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -9521,7 +9485,7 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -9534,10 +9498,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S98" t="b">
+        <v>1</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -9979,7 +9941,7 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>BD</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -9992,10 +9954,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S103" t="b">
+        <v>1</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -10075,7 +10035,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -10088,10 +10048,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S104" t="b">
+        <v>1</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -10909,7 +10867,7 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -10922,10 +10880,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S113" t="b">
+        <v>1</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -11460,7 +11416,7 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
@@ -11473,10 +11429,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S119" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S119" t="b">
+        <v>1</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -11645,7 +11599,7 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -11658,10 +11612,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S121" t="b">
+        <v>1</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -12381,7 +12333,7 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
@@ -12394,10 +12346,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S129" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S129" t="b">
+        <v>1</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -12566,7 +12516,7 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>CE</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
@@ -12579,10 +12529,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S131" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S131" t="b">
+        <v>1</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -12751,7 +12699,7 @@
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -12764,10 +12712,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S133" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S133" t="b">
+        <v>1</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -13292,7 +13238,7 @@
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
@@ -13305,10 +13251,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S139" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S139" t="b">
+        <v>1</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -14238,7 +14182,7 @@
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
@@ -14256,10 +14200,8 @@
           <t>2016_co_16_pm073.jpg</t>
         </is>
       </c>
-      <c r="S149" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S149" t="b">
+        <v>1</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
